--- a/script1/registered_scored.xlsx
+++ b/script1/registered_scored.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,17 +547,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Baldwin, Dan</t>
+          <t>Abel, Caiden</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DWBaldwin</t>
+          <t>1182664</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -581,17 +581,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>De, Sanchari</t>
+          <t>Baxter, Jessica</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SDe</t>
+          <t>JABaxter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -615,17 +615,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fuentes, Victor</t>
+          <t>Brewer, Courtney</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>vfuentesjr442</t>
+          <t>1180013</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -649,17 +649,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gallardo, Juan</t>
+          <t>Brewer, Elijah</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JGallardo</t>
+          <t>1183489</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -683,17 +683,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Harrell, chris</t>
+          <t>Cavazos, Elyssia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1181212</t>
+          <t>ecavazos</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -717,17 +717,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hearn, Jim</t>
+          <t>Deis, Sandra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>210438</t>
+          <t>SDeis</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -751,17 +751,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Le Morvan, Isaac</t>
+          <t>Dequillettes, Woody</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1181899</t>
+          <t>wdequillettes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -785,17 +785,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lehman, Nicholas</t>
+          <t>Desabrais, Duke</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1101620</t>
+          <t>DDDesabrais</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -819,17 +819,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mohammad, Ahmad</t>
+          <t>Fultz, Melissa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1111013</t>
+          <t>1182139</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -853,17 +853,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Patrick, Miranda</t>
+          <t>Graydon Jr., David</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1180745</t>
+          <t>1183337</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -887,17 +887,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Reiff, Zoe</t>
+          <t>Gross, Landon</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1180968</t>
+          <t>LRGross</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -921,17 +921,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Singh, Corey</t>
+          <t>Haile, Kokob</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CASingh</t>
+          <t>1104534</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -955,17 +955,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sofan, Mohammad</t>
+          <t>Huggins, Steve</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MSofan</t>
+          <t>1181516</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -989,17 +989,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Thomas, Scott</t>
+          <t>Ikonomakis, George</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1180589</t>
+          <t>196427</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1023,17 +1023,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ziha, Jaafar</t>
+          <t>Iqbal, Aban</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1099776</t>
+          <t>1100036</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>203091</t>
+          <t>1181094</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1047,13 +1047,931 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jabbour, Karim</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1181558</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Jatzke, Nicole</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1182885</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>K C, Himamsu</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>207477</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kedowide, Cyrian</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1102855</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Knox, Dakota</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1182538</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kuysters, Jordan</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1183254</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mace, Maria</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>202596</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Mancini, Meagan</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MMancini</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Massie, Dillon</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1180982</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Maxfield, Alisha</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1181978</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>McIvor, Bailey</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1182701</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Mestdagh, Karlee</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1103306</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Molinski, Vanessa</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>204560</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Nasrallah, Anthony</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1182739</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>O'Brien, Amy</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1182666</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Opdendries, Mike</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MOpdendries</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Percy, Taylor</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1182766</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Profiri, Ben</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1183553</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Schieber, Adam</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1114738</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Seelig, Bella</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1182770</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sharifi, Sherry</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>205653</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Smith, Beth</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1181616</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Tadesse, Elim</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1183461</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ushkowski, Logan</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1183136</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Velez, Javier</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1181908</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Williams, Ashley</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1182639</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Zubko, Kenzie</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1100036</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1181973</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/script1/registered_scored.xlsx
+++ b/script1/registered_scored.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,17 +547,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Abel, Caiden</t>
+          <t>Adebakin, Fikky</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1182664</t>
+          <t>207225</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -581,17 +581,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Baxter, Jessica</t>
+          <t>Albrecht, Shane</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JABaxter</t>
+          <t>1119561</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -615,17 +615,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brewer, Courtney</t>
+          <t>Andrews, Max</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1180013</t>
+          <t>1119521</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -649,17 +649,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brewer, Elijah</t>
+          <t>Aragon, Miguel</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1183489</t>
+          <t>1118794</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -683,17 +683,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cavazos, Elyssia</t>
+          <t>Argueta Gouveia, Claudia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ecavazos</t>
+          <t>197426</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -717,17 +717,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deis, Sandra</t>
+          <t>Arismendez, Joe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SDeis</t>
+          <t>JArismendez</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -751,17 +751,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dequillettes, Woody</t>
+          <t>Baker, Austen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>wdequillettes</t>
+          <t>1182201</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -785,17 +785,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Desabrais, Duke</t>
+          <t>Bardati, Nathan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DDDesabrais</t>
+          <t>1104774</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -819,17 +819,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fultz, Melissa</t>
+          <t>Baugh, Jeff</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1182139</t>
+          <t>1120272</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -853,17 +853,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Graydon Jr., David</t>
+          <t>Bedoya Hoyos, Juan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1183337</t>
+          <t>1119907</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -887,17 +887,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gross, Landon</t>
+          <t>Berard, Jon</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LRGross</t>
+          <t>186361</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -921,17 +921,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Haile, Kokob</t>
+          <t>Cardoso-Najera, Enrique</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1104534</t>
+          <t>1179722</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -955,17 +955,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Huggins, Steve</t>
+          <t>Carlson, Brooke</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1181516</t>
+          <t>1120225</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -989,17 +989,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ikonomakis, George</t>
+          <t>Castro, Sergio</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>196427</t>
+          <t>1119827</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1023,17 +1023,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Iqbal, Aban</t>
+          <t>Cerrato, Christopher</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1181094</t>
+          <t>1180796</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1057,17 +1057,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jabbour, Karim</t>
+          <t>Chopra, Jai</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1181558</t>
+          <t>1118923</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1091,17 +1091,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jatzke, Nicole</t>
+          <t>Cohn, Clayton</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1182885</t>
+          <t>cecohn</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -1125,17 +1125,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>K C, Himamsu</t>
+          <t>Conyers, John</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>207477</t>
+          <t>1119262</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1159,17 +1159,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kedowide, Cyrian</t>
+          <t>Cordova, Sylvia</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1102855</t>
+          <t>1119784</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1193,17 +1193,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Knox, Dakota</t>
+          <t>Corea, Cindy</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1182538</t>
+          <t>1119508</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1227,17 +1227,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kuysters, Jordan</t>
+          <t>CORTEZ, THEA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1183254</t>
+          <t>1119715</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1261,17 +1261,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mace, Maria</t>
+          <t>Curtis, Craig</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>202596</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1295,17 +1295,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mancini, Meagan</t>
+          <t>Dankowski, Ian</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MMancini</t>
+          <t>1117758</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -1329,17 +1329,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Massie, Dillon</t>
+          <t>Davila, Brittney</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1180982</t>
+          <t>1111792</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1363,17 +1363,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Maxfield, Alisha</t>
+          <t>De Aro, Abbigail</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1181978</t>
+          <t>1119842</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1397,17 +1397,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>McIvor, Bailey</t>
+          <t>DeMelo, Fermino</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1182701</t>
+          <t>1119219</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1431,17 +1431,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mestdagh, Karlee</t>
+          <t>Di Pietro, Elliott</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1103306</t>
+          <t>1118294</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1465,17 +1465,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Molinski, Vanessa</t>
+          <t>Elmer, Lamon</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>204560</t>
+          <t>1118429</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1499,17 +1499,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nasrallah, Anthony</t>
+          <t>Fachin, Pedro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1182739</t>
+          <t>1116675</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1533,17 +1533,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>O'Brien, Amy</t>
+          <t>Felzien, Aidan</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1182666</t>
+          <t>ADFelzien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1567,17 +1567,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Opdendries, Mike</t>
+          <t>Fernandez, Liam</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MOpdendries</t>
+          <t>1111857</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -1601,17 +1601,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Percy, Taylor</t>
+          <t>Franklin, Mitchell</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1182766</t>
+          <t>1118623</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Profiri, Ben</t>
+          <t>Galarza, Hector</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1183553</t>
+          <t>204454</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1669,17 +1669,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Schieber, Adam</t>
+          <t>Geraldo, Jorge</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1114738</t>
+          <t>JGeraldo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1703,17 +1703,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Seelig, Bella</t>
+          <t>Gong, Max</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1182770</t>
+          <t>1119014</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -1737,17 +1737,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sharifi, Sherry</t>
+          <t>Gonzalez, Dominic</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>205653</t>
+          <t>197960</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -1771,17 +1771,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Smith, Beth</t>
+          <t>Gordillo, Hugo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1181616</t>
+          <t>hgordillo265</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -1805,17 +1805,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tadesse, Elim</t>
+          <t>Guan, Alex</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1183461</t>
+          <t>1118125</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1839,17 +1839,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ushkowski, Logan</t>
+          <t>Guzman, Destiny</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1183136</t>
+          <t>208097</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Velez, Javier</t>
+          <t>Habacon, Raphael</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1181908</t>
+          <t>rhabacon239</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1907,17 +1907,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Williams, Ashley</t>
+          <t>Hanna, Maged</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1182639</t>
+          <t>208255</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1941,17 +1941,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Zubko, Kenzie</t>
+          <t>Harakal, Matthew</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1100036</t>
+          <t>1099780</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1181973</t>
+          <t>mharakal781</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1972,6 +1972,3134 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Hassen, Shelley</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>209101</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Hayes, Kourtney</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1180595</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Hegwer, Jon</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1178913</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Hernandez, Daniel</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1119906</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Hess, Nicklaus</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1119097</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Hession, Sean</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1119245</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Hilts, Isaiah</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1119452</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Hood, Mitchell</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>195926</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Hsiao, Kevin</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>206566</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Hussein, Abdi</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1120235</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Inanc, Atakan</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AInanc</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Iqbal, Aban</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1181094</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Jang, Cindy</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>205340</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Jensen, Matt</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1178886</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Johnson, Michael</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1115304</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Jones, Matt</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1119866</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jovanova, Daniela</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>200348</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Keller, Chase</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1181563</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Laudon, Grier</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1118334</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Laxdal, Larry</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>llaxdal</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Leal, Armando</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>204325</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Lemus Aldana, Adriana</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1119925</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Leon, Alan</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1112516</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Lui, Terri</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1119032</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Markusen, Stephen</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1120016</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Martin, Jeremie</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1179695</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MCPHERSON, ALLAN</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1118819</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Meneses, Osvaldo</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>197231</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Moline, Alec</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1119803</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Morales Lora, Jose</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1119314</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MOYA VERDUZCO, DANIEL</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1111749</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Mundy, Richard</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>201932</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Murillo, Ruben</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1119814</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Najera, Sharon</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1179609</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Newberry, Emily</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>EANewberry</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Odchigue, Chris</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>186416</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Oliveira, Alexia</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>206697</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Onyschuk, Ken</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1119702</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Ortegon, Elvia</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1119185</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Owen, Maria</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1118119</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Ozawa, Russell</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1105276</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Padgett, Matt</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1119104</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Papalazarou, Ilias-Alexandros</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1118778</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Parlberg, John</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1116610</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Pepple, Tamunoibim</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1119160</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Perez Duarte, Loida</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1120323</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Perlas, Iriz</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1118934</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Pinell, Marcelo</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1180099</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Plante, Lisa</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>laplante</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Pyper, Joe</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1119586</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Rehman, Sikandar</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1115913</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Reyes, Carlos</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>208053</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Rezai, Kian</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1179367</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Rivera, Jaime</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1119958</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Robinson, Russell</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>209565</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Rodriguez Flores, Luis</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>202129</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Rojas, Uciel</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1119855</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Russell, Cody</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CARussell</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Saini, Sanjeev</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1119334</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Salinas, Miguel</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>msalinas525</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Samuelsen, Alexis</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1118820</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Saric, Kyle</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>1118412</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Schieber, Adam</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>1114738</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Schindelka, Ryan</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>RJSchindelka</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Schweigert, Sean</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>1178417</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Scott, Lani</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>LScott</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sekyi, Theo</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>1179240</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Shamshiri, Kasra</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1179103</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Simpson, John</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>jnsimpson</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Singh, Gurpreet</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1118414</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Skogquist, Tucker</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1179804</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sultan Murad, Soniya</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>1118799</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>THOMPSON, JOSEPH</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>1119592</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Tinoco-Torales, Beatriz</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>1105095</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Tobin, Riley</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>112673</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Tocci, Sarah</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>1179595</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Torabifar, Samaneh</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>1120269</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Torrence, Ken</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>1105243</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>UGALDE OSORNIO, ESTEBAN</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>1118860</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Vielma, Yadie</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>1118714</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Villalobos Ortiz, Daniel</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>1119985</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Ward, Trevor</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>1117742</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Waugh, Brendan</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>bwaugh608</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Wells, Scott</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>1119438</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Welsh, Ian</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>1118872</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Wey, Clarissa</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>1112490</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Wingate, Peter</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>1114707</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Wolford, Brian</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>196078</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Yepez, Wendy</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>1119871</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Young, Kevin</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>205487</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Zepeda Jr, Staffan</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>1119980</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Zullo, Zachary</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1099780</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>1119537</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
